--- a/assets/returns/Market Risk Analysis.xlsx
+++ b/assets/returns/Market Risk Analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0997F4B-8CEC-4589-9DD9-8F22717E7DA2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D0DB57-F2A0-4C32-9DC8-FC138437DA58}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Risk Analysis" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -18,6 +18,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -60,9 +64,6 @@
     <t>5% of years will have a loss worst than r</t>
   </si>
   <si>
-    <t>7.5%-?=</t>
-  </si>
-  <si>
     <t>P(r&lt;-5)=</t>
   </si>
   <si>
@@ -75,9 +76,6 @@
     <t>P(-5&lt;r&lt;5)=</t>
   </si>
   <si>
-    <t>10%=P(7.5-x&lt;r&lt;7.5+x)</t>
-  </si>
-  <si>
     <t>10%=P(r&gt;?)</t>
   </si>
   <si>
@@ -88,28 +86,26 @@
   </si>
   <si>
     <t>UB=</t>
+  </si>
+  <si>
+    <t>12%-?=</t>
+  </si>
+  <si>
+    <t>10%=P(12-x&lt;r&lt;12+x)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -162,45 +158,41 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -210,11 +202,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -504,164 +496,164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6CFF529-8AE5-449B-BB0B-FA6BDA9299BE}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultColWidth="6.62890625" defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="6.6328125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.7890625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.9453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.89453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.83984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.26171875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="58.1015625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.47265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.20703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="31" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.89453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.3125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="6.62890625" style="2"/>
+    <col min="10" max="10" width="3.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="6.6328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11">
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.6">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>0.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A5" s="16" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A6" s="16" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A7" s="16" t="s">
-        <v>15</v>
-      </c>
       <c r="B7" s="9"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A9" s="18" t="s">
-        <v>18</v>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="14"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A10" s="18" t="s">
-        <v>17</v>
+      <c r="C9" s="12"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="16" t="s">
+        <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="14"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="C10" s="12"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D11" s="5"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A12" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="17"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="B13" s="16" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="15"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="15"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="C13" s="13"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C16" s="4"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="15"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A19" s="24" t="s">
+      <c r="C17" s="13"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A20" s="19" t="s">
-        <v>19</v>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="17" t="s">
+        <v>17</v>
       </c>
       <c r="B20" s="10"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A21" s="20" t="s">
-        <v>20</v>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="18" t="s">
+        <v>18</v>
       </c>
       <c r="B21" s="10"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A23" s="22" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="22"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="B23" s="20"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B24" s="8"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
@@ -669,23 +661,23 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="21"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="B27" s="19"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="7"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="B29" s="7"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>1</v>
       </c>
